--- a/data/ScannerData.xlsx
+++ b/data/ScannerData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shenoytech.DESKTOP-6AVSU7L\Desktop\RSI(2) above 99 Scan\rsi_scanner8\rsi_scanner\sample_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shenoytech.DESKTOP-6AVSU7L\Desktop\intraday breakout Scanner\intraday_breakout_flask_1m_scanfix\intraday_breakout_flask\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2ACB1E6-E13F-4646-84AA-C025C3A6E933}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DECCB2FA-ECB9-4C2E-A9F5-E4C712F9E30B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1716" uniqueCount="760">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1712" uniqueCount="760">
   <si>
     <t>POWERGRID.NS</t>
   </si>
@@ -5400,7 +5400,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10E86D90-5A7F-4C6D-8083-62829FC2BFA4}">
-  <dimension ref="A1:A421"/>
+  <dimension ref="A1:A417"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -6445,1066 +6445,1046 @@
     </row>
     <row r="209" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>586</v>
+        <v>399</v>
       </c>
     </row>
     <row r="210" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="211" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="212" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>401</v>
+        <v>587</v>
       </c>
     </row>
     <row r="213" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>587</v>
+        <v>402</v>
       </c>
     </row>
     <row r="214" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="215" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>403</v>
+        <v>588</v>
       </c>
     </row>
     <row r="216" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>588</v>
+        <v>405</v>
       </c>
     </row>
     <row r="217" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="218" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="219" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="220" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="221" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>412</v>
+        <v>591</v>
       </c>
     </row>
     <row r="222" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="223" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>592</v>
+        <v>413</v>
       </c>
     </row>
     <row r="224" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>413</v>
+        <v>204</v>
       </c>
     </row>
     <row r="225" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>204</v>
+        <v>593</v>
       </c>
     </row>
     <row r="226" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="227" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="228" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>595</v>
+        <v>191</v>
       </c>
     </row>
     <row r="229" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>191</v>
+        <v>418</v>
       </c>
     </row>
     <row r="230" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>418</v>
+        <v>596</v>
       </c>
     </row>
     <row r="231" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>596</v>
+        <v>419</v>
       </c>
     </row>
     <row r="232" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>419</v>
+        <v>598</v>
       </c>
     </row>
     <row r="233" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="234" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="235" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="236" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>601</v>
+        <v>423</v>
       </c>
     </row>
     <row r="237" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="238" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>424</v>
+        <v>602</v>
       </c>
     </row>
     <row r="239" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>602</v>
+        <v>425</v>
       </c>
     </row>
     <row r="240" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>425</v>
+        <v>603</v>
       </c>
     </row>
     <row r="241" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>603</v>
+        <v>97</v>
       </c>
     </row>
     <row r="242" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>97</v>
+        <v>426</v>
       </c>
     </row>
     <row r="243" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>426</v>
+        <v>604</v>
       </c>
     </row>
     <row r="244" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="245" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>605</v>
+        <v>428</v>
       </c>
     </row>
     <row r="246" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>428</v>
+        <v>606</v>
       </c>
     </row>
     <row r="247" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>606</v>
+        <v>429</v>
       </c>
     </row>
     <row r="248" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="249" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="250" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>431</v>
+        <v>607</v>
       </c>
     </row>
     <row r="251" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="252" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="253" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>609</v>
+        <v>432</v>
       </c>
     </row>
     <row r="254" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="255" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="256" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="257" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>433</v>
+        <v>613</v>
       </c>
     </row>
     <row r="258" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="259" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="260" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="261" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>615</v>
+        <v>435</v>
       </c>
     </row>
     <row r="262" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="263" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>435</v>
+        <v>618</v>
       </c>
     </row>
     <row r="264" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="265" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>618</v>
+        <v>436</v>
       </c>
     </row>
     <row r="266" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>619</v>
+        <v>437</v>
       </c>
     </row>
     <row r="267" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>436</v>
+        <v>620</v>
       </c>
     </row>
     <row r="268" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="269" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>620</v>
+        <v>441</v>
       </c>
     </row>
     <row r="270" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>440</v>
+        <v>621</v>
       </c>
     </row>
     <row r="271" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>441</v>
+        <v>622</v>
       </c>
     </row>
     <row r="272" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>621</v>
+        <v>443</v>
       </c>
     </row>
     <row r="273" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>622</v>
+        <v>444</v>
       </c>
     </row>
     <row r="274" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>443</v>
+        <v>623</v>
       </c>
     </row>
     <row r="275" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>444</v>
+        <v>67</v>
       </c>
     </row>
     <row r="276" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>623</v>
+        <v>1</v>
       </c>
     </row>
     <row r="277" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>67</v>
+        <v>625</v>
       </c>
     </row>
     <row r="278" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>1</v>
+        <v>445</v>
       </c>
     </row>
     <row r="279" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>625</v>
+        <v>446</v>
       </c>
     </row>
     <row r="280" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>445</v>
+        <v>626</v>
       </c>
     </row>
     <row r="281" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="282" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="283" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="284" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
     </row>
     <row r="285" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
     </row>
     <row r="286" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>449</v>
+        <v>633</v>
       </c>
     </row>
     <row r="287" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>631</v>
+        <v>450</v>
       </c>
     </row>
     <row r="288" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
     </row>
     <row r="289" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>633</v>
+        <v>452</v>
       </c>
     </row>
     <row r="290" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>450</v>
+        <v>636</v>
       </c>
     </row>
     <row r="291" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>635</v>
+        <v>453</v>
       </c>
     </row>
     <row r="292" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="293" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="294" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="295" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="296" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="297" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>455</v>
+        <v>641</v>
       </c>
     </row>
     <row r="298" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="299" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="300" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>641</v>
+        <v>459</v>
       </c>
     </row>
     <row r="301" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>458</v>
+        <v>643</v>
       </c>
     </row>
     <row r="302" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>642</v>
+        <v>461</v>
       </c>
     </row>
     <row r="303" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>459</v>
+        <v>645</v>
       </c>
     </row>
     <row r="304" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
     </row>
     <row r="305" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>461</v>
+        <v>647</v>
       </c>
     </row>
     <row r="306" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>645</v>
+        <v>464</v>
       </c>
     </row>
     <row r="307" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="308" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>647</v>
+        <v>465</v>
       </c>
     </row>
     <row r="309" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="310" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>648</v>
+        <v>468</v>
       </c>
     </row>
     <row r="311" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="312" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>466</v>
+        <v>650</v>
       </c>
     </row>
     <row r="313" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>467</v>
+        <v>651</v>
       </c>
     </row>
     <row r="314" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="315" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>469</v>
+        <v>654</v>
       </c>
     </row>
     <row r="316" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
     </row>
     <row r="317" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
     </row>
     <row r="318" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>470</v>
+        <v>657</v>
       </c>
     </row>
     <row r="319" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>654</v>
+        <v>95</v>
       </c>
     </row>
     <row r="320" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>655</v>
+        <v>471</v>
       </c>
     </row>
     <row r="321" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>656</v>
+        <v>472</v>
       </c>
     </row>
     <row r="322" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
     </row>
     <row r="323" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>95</v>
+        <v>661</v>
       </c>
     </row>
     <row r="324" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="325" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>472</v>
+        <v>663</v>
       </c>
     </row>
     <row r="326" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
     </row>
     <row r="327" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>661</v>
+        <v>666</v>
       </c>
     </row>
     <row r="328" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>473</v>
+        <v>667</v>
       </c>
     </row>
     <row r="329" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
     </row>
     <row r="330" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
     </row>
     <row r="331" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>666</v>
+        <v>476</v>
       </c>
     </row>
     <row r="332" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>667</v>
+        <v>154</v>
       </c>
     </row>
     <row r="333" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>668</v>
+        <v>477</v>
       </c>
     </row>
     <row r="334" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>669</v>
+        <v>208</v>
       </c>
     </row>
     <row r="335" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="336" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>154</v>
+        <v>672</v>
       </c>
     </row>
     <row r="337" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>477</v>
+        <v>673</v>
       </c>
     </row>
     <row r="338" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>208</v>
+        <v>674</v>
       </c>
     </row>
     <row r="339" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>479</v>
+        <v>675</v>
       </c>
     </row>
     <row r="340" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
     </row>
     <row r="341" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>673</v>
+        <v>2</v>
       </c>
     </row>
     <row r="342" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
     </row>
     <row r="343" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>675</v>
+        <v>481</v>
       </c>
     </row>
     <row r="344" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="345" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="346" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
     </row>
     <row r="347" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>481</v>
+        <v>682</v>
       </c>
     </row>
     <row r="348" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>678</v>
+        <v>482</v>
       </c>
     </row>
     <row r="349" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>15</v>
+        <v>683</v>
       </c>
     </row>
     <row r="350" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
     </row>
     <row r="351" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
     </row>
     <row r="352" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>482</v>
+        <v>687</v>
       </c>
     </row>
     <row r="353" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
     </row>
     <row r="354" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
     </row>
     <row r="355" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
     </row>
     <row r="356" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="357" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
     </row>
     <row r="358" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
     </row>
     <row r="359" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
     </row>
     <row r="360" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>691</v>
+        <v>486</v>
       </c>
     </row>
     <row r="361" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>692</v>
+        <v>487</v>
       </c>
     </row>
     <row r="362" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>693</v>
+        <v>488</v>
       </c>
     </row>
     <row r="363" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="364" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>486</v>
+        <v>696</v>
       </c>
     </row>
     <row r="365" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="366" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>488</v>
+        <v>698</v>
       </c>
     </row>
     <row r="367" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
     </row>
     <row r="368" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>696</v>
+        <v>701</v>
       </c>
     </row>
     <row r="369" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>489</v>
+        <v>702</v>
       </c>
     </row>
     <row r="370" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
     </row>
     <row r="371" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
     </row>
     <row r="372" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
     </row>
     <row r="373" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
     </row>
     <row r="374" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
     </row>
     <row r="375" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>704</v>
+        <v>492</v>
       </c>
     </row>
     <row r="376" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>705</v>
+        <v>493</v>
       </c>
     </row>
     <row r="377" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
     </row>
     <row r="378" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
     </row>
     <row r="379" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="380" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>493</v>
+        <v>711</v>
       </c>
     </row>
     <row r="381" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
     </row>
     <row r="382" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
     </row>
     <row r="383" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>494</v>
+        <v>714</v>
       </c>
     </row>
     <row r="384" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>711</v>
+        <v>716</v>
       </c>
     </row>
     <row r="385" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>712</v>
+        <v>717</v>
       </c>
     </row>
     <row r="386" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>713</v>
+        <v>718</v>
       </c>
     </row>
     <row r="387" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>714</v>
+        <v>719</v>
       </c>
     </row>
     <row r="388" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>716</v>
+        <v>496</v>
       </c>
     </row>
     <row r="389" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>717</v>
+        <v>722</v>
       </c>
     </row>
     <row r="390" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>718</v>
+        <v>723</v>
       </c>
     </row>
     <row r="391" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>719</v>
+        <v>497</v>
       </c>
     </row>
     <row r="392" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>496</v>
+        <v>725</v>
       </c>
     </row>
     <row r="393" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
     </row>
     <row r="394" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>723</v>
+        <v>498</v>
       </c>
     </row>
     <row r="395" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>497</v>
+        <v>727</v>
       </c>
     </row>
     <row r="396" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
     </row>
     <row r="397" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>726</v>
+        <v>499</v>
       </c>
     </row>
     <row r="398" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>498</v>
+        <v>730</v>
       </c>
     </row>
     <row r="399" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
     </row>
     <row r="400" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>728</v>
+        <v>733</v>
       </c>
     </row>
     <row r="401" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>499</v>
+        <v>734</v>
       </c>
     </row>
     <row r="402" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="403" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>731</v>
+        <v>737</v>
       </c>
     </row>
     <row r="404" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
     </row>
     <row r="405" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
     </row>
     <row r="406" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>735</v>
+        <v>501</v>
       </c>
     </row>
     <row r="407" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
     </row>
     <row r="408" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
     </row>
     <row r="409" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
     </row>
     <row r="410" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>501</v>
+        <v>745</v>
       </c>
     </row>
     <row r="411" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
     </row>
     <row r="412" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
     </row>
     <row r="413" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>744</v>
+        <v>759</v>
       </c>
     </row>
     <row r="414" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>745</v>
+        <v>252</v>
       </c>
     </row>
     <row r="415" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>746</v>
+        <v>340</v>
       </c>
     </row>
     <row r="416" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>747</v>
+        <v>377</v>
       </c>
     </row>
     <row r="417" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="418" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A418" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="419" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A419" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="420" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A420" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="421" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A421" t="s">
         <v>137</v>
       </c>
     </row>
